--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665E8450-615A-484A-94B2-93073E1F81F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5627E79-2307-4AAA-96D5-6F40CBA8C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="1050" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32595" yWindow="2160" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="396">
   <si>
     <t>Product</t>
   </si>
@@ -1121,13 +1121,100 @@
   </si>
   <si>
     <t>£2756.16</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>TB4020</t>
+  </si>
+  <si>
+    <t>25mm Celotex</t>
+  </si>
+  <si>
+    <t>30mm Celotex</t>
+  </si>
+  <si>
+    <t>40mm Celotex</t>
+  </si>
+  <si>
+    <t>50mm Celotex</t>
+  </si>
+  <si>
+    <t>60mm Celotex</t>
+  </si>
+  <si>
+    <t>70mm Celotex</t>
+  </si>
+  <si>
+    <t>75mm Celotex</t>
+  </si>
+  <si>
+    <t>80mm Celotex</t>
+  </si>
+  <si>
+    <t>90mm Celotex</t>
+  </si>
+  <si>
+    <t>100mm Celotex</t>
+  </si>
+  <si>
+    <t>110mm Celotex</t>
+  </si>
+  <si>
+    <t>120mm Celotex</t>
+  </si>
+  <si>
+    <t>130mm Celotex</t>
+  </si>
+  <si>
+    <t>140mm Celotex</t>
+  </si>
+  <si>
+    <t>150mm Celotex</t>
+  </si>
+  <si>
+    <t>165mm Celotex1</t>
+  </si>
+  <si>
+    <t>xr4200pal</t>
+  </si>
+  <si>
+    <t>PL4025</t>
+  </si>
+  <si>
+    <t>PL4040</t>
+  </si>
+  <si>
+    <t>PL4050</t>
+  </si>
+  <si>
+    <t>PL4060</t>
+  </si>
+  <si>
+    <t>celcav50</t>
+  </si>
+  <si>
+    <t>cw40755</t>
+  </si>
+  <si>
+    <t>celcav85</t>
+  </si>
+  <si>
+    <t>cw4100</t>
+  </si>
+  <si>
+    <t>CELOTC1090</t>
+  </si>
+  <si>
+    <t>CELOTC1115</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,6 +1229,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1179,9 +1271,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1492,8 +1587,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>292</v>
+      <c r="A1" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1549,7 +1644,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -1605,7 +1700,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>369</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -1661,7 +1756,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>370</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1717,7 +1812,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -1773,7 +1868,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>372</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -1829,7 +1924,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>373</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -1885,7 +1980,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>374</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1941,7 +2036,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -1997,7 +2092,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -2053,7 +2148,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -2109,7 +2204,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>378</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
@@ -2165,7 +2260,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>301</v>
+        <v>379</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
@@ -2221,7 +2316,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>380</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -2277,7 +2372,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>381</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2333,7 +2428,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>382</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -2389,7 +2484,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -2445,7 +2540,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>384</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -2501,7 +2596,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
@@ -2557,7 +2652,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>305</v>
+        <v>386</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -2613,7 +2708,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>306</v>
+        <v>387</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -2669,7 +2764,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>307</v>
+        <v>388</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -2725,7 +2820,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>308</v>
+        <v>389</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
@@ -2781,7 +2876,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>308</v>
+        <v>390</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
@@ -2837,7 +2932,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>391</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
@@ -2893,7 +2988,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -2949,7 +3044,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>310</v>
+        <v>393</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
@@ -3005,7 +3100,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>311</v>
+        <v>394</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
@@ -3061,7 +3156,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>312</v>
+        <v>395</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5627E79-2307-4AAA-96D5-6F40CBA8C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C798D3F-C7F6-457C-8EAF-5BDA86E86DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32595" yWindow="2160" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30765" yWindow="1740" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="398">
   <si>
     <t>Product</t>
   </si>
@@ -712,63 +712,12 @@
     <t>£14.25</t>
   </si>
   <si>
-    <t>£16.89</t>
-  </si>
-  <si>
-    <t>£20.30</t>
-  </si>
-  <si>
-    <t>£21.99</t>
-  </si>
-  <si>
-    <t>£26.99</t>
-  </si>
-  <si>
-    <t>£29.98</t>
-  </si>
-  <si>
-    <t>£28.98</t>
-  </si>
-  <si>
-    <t>£33.49</t>
-  </si>
-  <si>
     <t>£36.99</t>
   </si>
   <si>
-    <t>£37.49</t>
-  </si>
-  <si>
-    <t>£45.25</t>
-  </si>
-  <si>
     <t>£54.99</t>
   </si>
   <si>
-    <t>£56.50</t>
-  </si>
-  <si>
-    <t>£55.75</t>
-  </si>
-  <si>
-    <t>£947.88</t>
-  </si>
-  <si>
-    <t>£1230.0</t>
-  </si>
-  <si>
-    <t>£40.50</t>
-  </si>
-  <si>
-    <t>£49.99</t>
-  </si>
-  <si>
-    <t>£53.10</t>
-  </si>
-  <si>
-    <t>£59.10</t>
-  </si>
-  <si>
     <t>£1727.84</t>
   </si>
   <si>
@@ -1208,6 +1157,63 @@
   </si>
   <si>
     <t>CELOTC1115</t>
+  </si>
+  <si>
+    <t>£14.99</t>
+  </si>
+  <si>
+    <t>£13.90</t>
+  </si>
+  <si>
+    <t>£16.35</t>
+  </si>
+  <si>
+    <t>£19.99</t>
+  </si>
+  <si>
+    <t>£21.49</t>
+  </si>
+  <si>
+    <t>£25.99</t>
+  </si>
+  <si>
+    <t>£29.75</t>
+  </si>
+  <si>
+    <t>£28.49</t>
+  </si>
+  <si>
+    <t>£32.99</t>
+  </si>
+  <si>
+    <t>£45.50</t>
+  </si>
+  <si>
+    <t>£44.50</t>
+  </si>
+  <si>
+    <t>£53.50</t>
+  </si>
+  <si>
+    <t>£54.25</t>
+  </si>
+  <si>
+    <t>£899.88</t>
+  </si>
+  <si>
+    <t>£1199.88</t>
+  </si>
+  <si>
+    <t>£39.99</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£52.50</t>
+  </si>
+  <si>
+    <t>£57.40</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1644,7 +1650,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -1659,7 +1665,7 @@
         <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
         <v>78</v>
@@ -1686,10 +1692,10 @@
         <v>206</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>379</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="Q2" t="s">
         <v>76</v>
@@ -1700,7 +1706,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -1727,7 +1733,7 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="K3" t="s">
         <v>152</v>
@@ -1742,21 +1748,21 @@
         <v>207</v>
       </c>
       <c r="O3" t="s">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="P3" t="s">
         <v>48</v>
       </c>
       <c r="Q3" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="R3" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1771,7 +1777,7 @@
         <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G4" t="s">
         <v>80</v>
@@ -1783,7 +1789,7 @@
         <v>126</v>
       </c>
       <c r="J4" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="K4" t="s">
         <v>153</v>
@@ -1798,21 +1804,21 @@
         <v>208</v>
       </c>
       <c r="O4" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="Q4" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="R4" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
@@ -1827,7 +1833,7 @@
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G5" t="s">
         <v>81</v>
@@ -1839,7 +1845,7 @@
         <v>127</v>
       </c>
       <c r="J5" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="K5" t="s">
         <v>154</v>
@@ -1854,21 +1860,21 @@
         <v>209</v>
       </c>
       <c r="O5" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
       <c r="P5" t="s">
         <v>50</v>
       </c>
       <c r="Q5" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="R5" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -1883,7 +1889,7 @@
         <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="G6" t="s">
         <v>82</v>
@@ -1895,7 +1901,7 @@
         <v>128</v>
       </c>
       <c r="J6" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="K6" t="s">
         <v>155</v>
@@ -1910,21 +1916,21 @@
         <v>210</v>
       </c>
       <c r="O6" t="s">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="P6" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="Q6" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="R6" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -1939,7 +1945,7 @@
         <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="G7" t="s">
         <v>83</v>
@@ -1951,7 +1957,7 @@
         <v>129</v>
       </c>
       <c r="J7" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="K7" t="s">
         <v>156</v>
@@ -1966,21 +1972,21 @@
         <v>211</v>
       </c>
       <c r="O7" t="s">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="P7" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="Q7" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="R7" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1995,7 +2001,7 @@
         <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="G8" t="s">
         <v>54</v>
@@ -2007,7 +2013,7 @@
         <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="K8" t="s">
         <v>157</v>
@@ -2022,21 +2028,21 @@
         <v>212</v>
       </c>
       <c r="O8" t="s">
-        <v>234</v>
+        <v>385</v>
       </c>
       <c r="P8" t="s">
         <v>53</v>
       </c>
       <c r="Q8" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="R8" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -2051,7 +2057,7 @@
         <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="G9" t="s">
         <v>84</v>
@@ -2063,7 +2069,7 @@
         <v>131</v>
       </c>
       <c r="J9" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="K9" t="s">
         <v>158</v>
@@ -2078,21 +2084,21 @@
         <v>213</v>
       </c>
       <c r="O9" t="s">
-        <v>235</v>
+        <v>386</v>
       </c>
       <c r="P9" t="s">
         <v>54</v>
       </c>
       <c r="Q9" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="R9" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -2107,7 +2113,7 @@
         <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="G10" t="s">
         <v>85</v>
@@ -2119,7 +2125,7 @@
         <v>132</v>
       </c>
       <c r="J10" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="K10" t="s">
         <v>159</v>
@@ -2134,21 +2140,21 @@
         <v>214</v>
       </c>
       <c r="O10" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="Q10" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="R10" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -2163,7 +2169,7 @@
         <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G11" t="s">
         <v>86</v>
@@ -2175,7 +2181,7 @@
         <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="K11" t="s">
         <v>160</v>
@@ -2190,21 +2196,21 @@
         <v>215</v>
       </c>
       <c r="O11" t="s">
-        <v>237</v>
+        <v>56</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="Q11" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="R11" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
@@ -2219,7 +2225,7 @@
         <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G12" t="s">
         <v>87</v>
@@ -2231,7 +2237,7 @@
         <v>134</v>
       </c>
       <c r="J12" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="K12" t="s">
         <v>161</v>
@@ -2246,21 +2252,21 @@
         <v>216</v>
       </c>
       <c r="O12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P12" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="Q12" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="R12" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
@@ -2275,7 +2281,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="G13" t="s">
         <v>88</v>
@@ -2287,7 +2293,7 @@
         <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="K13" t="s">
         <v>162</v>
@@ -2302,21 +2308,21 @@
         <v>217</v>
       </c>
       <c r="O13" t="s">
-        <v>58</v>
+        <v>388</v>
       </c>
       <c r="P13" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="Q13" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="R13" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -2331,7 +2337,7 @@
         <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="G14" t="s">
         <v>89</v>
@@ -2343,7 +2349,7 @@
         <v>136</v>
       </c>
       <c r="J14" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="K14" t="s">
         <v>89</v>
@@ -2358,21 +2364,21 @@
         <v>218</v>
       </c>
       <c r="O14" t="s">
-        <v>239</v>
+        <v>389</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="Q14" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="R14" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2387,7 +2393,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="G15" t="s">
         <v>90</v>
@@ -2399,7 +2405,7 @@
         <v>137</v>
       </c>
       <c r="J15" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="K15" t="s">
         <v>163</v>
@@ -2414,21 +2420,21 @@
         <v>219</v>
       </c>
       <c r="O15" t="s">
-        <v>240</v>
+        <v>390</v>
       </c>
       <c r="P15" t="s">
         <v>60</v>
       </c>
       <c r="Q15" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="R15" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -2455,7 +2461,7 @@
         <v>138</v>
       </c>
       <c r="J16" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="K16" t="s">
         <v>164</v>
@@ -2470,13 +2476,13 @@
         <v>220</v>
       </c>
       <c r="O16" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="P16" t="s">
         <v>61</v>
       </c>
       <c r="Q16" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="R16" t="s">
         <v>76</v>
@@ -2484,7 +2490,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -2511,7 +2517,7 @@
         <v>139</v>
       </c>
       <c r="J17" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="K17" t="s">
         <v>165</v>
@@ -2526,21 +2532,21 @@
         <v>221</v>
       </c>
       <c r="O17" t="s">
-        <v>242</v>
+        <v>391</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="Q17" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="R17" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -2555,7 +2561,7 @@
         <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="G18" t="s">
         <v>76</v>
@@ -2582,13 +2588,13 @@
         <v>222</v>
       </c>
       <c r="O18" t="s">
-        <v>243</v>
+        <v>392</v>
       </c>
       <c r="P18" t="s">
         <v>63</v>
       </c>
       <c r="Q18" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="R18" t="s">
         <v>76</v>
@@ -2596,7 +2602,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
@@ -2623,7 +2629,7 @@
         <v>141</v>
       </c>
       <c r="J19" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="K19" t="s">
         <v>167</v>
@@ -2638,21 +2644,21 @@
         <v>223</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>393</v>
       </c>
       <c r="P19" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="Q19" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="R19" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -2667,7 +2673,7 @@
         <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="G20" t="s">
         <v>94</v>
@@ -2679,7 +2685,7 @@
         <v>142</v>
       </c>
       <c r="J20" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="K20" t="s">
         <v>168</v>
@@ -2694,21 +2700,21 @@
         <v>224</v>
       </c>
       <c r="O20" t="s">
-        <v>245</v>
+        <v>394</v>
       </c>
       <c r="P20" t="s">
         <v>65</v>
       </c>
       <c r="Q20" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="R20" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -2723,7 +2729,7 @@
         <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="G21" t="s">
         <v>95</v>
@@ -2735,7 +2741,7 @@
         <v>138</v>
       </c>
       <c r="J21" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="K21" t="s">
         <v>169</v>
@@ -2750,21 +2756,21 @@
         <v>224</v>
       </c>
       <c r="O21" t="s">
-        <v>246</v>
+        <v>395</v>
       </c>
       <c r="P21" t="s">
         <v>66</v>
       </c>
       <c r="Q21" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="R21" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -2779,7 +2785,7 @@
         <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="G22" t="s">
         <v>96</v>
@@ -2791,7 +2797,7 @@
         <v>143</v>
       </c>
       <c r="J22" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="K22" t="s">
         <v>170</v>
@@ -2806,21 +2812,21 @@
         <v>224</v>
       </c>
       <c r="O22" t="s">
-        <v>247</v>
+        <v>396</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="Q22" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="R22" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B23" t="s">
         <v>39</v>
@@ -2835,7 +2841,7 @@
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="G23" t="s">
         <v>97</v>
@@ -2847,7 +2853,7 @@
         <v>144</v>
       </c>
       <c r="J23" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="K23" t="s">
         <v>171</v>
@@ -2859,24 +2865,24 @@
         <v>198</v>
       </c>
       <c r="N23" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="O23" t="s">
-        <v>248</v>
+        <v>397</v>
       </c>
       <c r="P23" t="s">
         <v>68</v>
       </c>
       <c r="Q23" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="R23" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="B24" t="s">
         <v>40</v>
@@ -2891,7 +2897,7 @@
         <v>69</v>
       </c>
       <c r="F24" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="G24" t="s">
         <v>76</v>
@@ -2903,7 +2909,7 @@
         <v>145</v>
       </c>
       <c r="J24" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="K24" t="s">
         <v>172</v>
@@ -2924,15 +2930,15 @@
         <v>69</v>
       </c>
       <c r="Q24" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="R24" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B25" t="s">
         <v>41</v>
@@ -2947,7 +2953,7 @@
         <v>70</v>
       </c>
       <c r="F25" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="G25" t="s">
         <v>76</v>
@@ -2959,7 +2965,7 @@
         <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="K25" t="s">
         <v>172</v>
@@ -2980,15 +2986,15 @@
         <v>70</v>
       </c>
       <c r="Q25" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="R25" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -3015,7 +3021,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="K26" t="s">
         <v>76</v>
@@ -3044,7 +3050,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
@@ -3059,7 +3065,7 @@
         <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="G27" t="s">
         <v>76</v>
@@ -3071,7 +3077,7 @@
         <v>147</v>
       </c>
       <c r="J27" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="K27" t="s">
         <v>173</v>
@@ -3092,15 +3098,15 @@
         <v>72</v>
       </c>
       <c r="Q27" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="R27" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
@@ -3115,7 +3121,7 @@
         <v>73</v>
       </c>
       <c r="F28" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G28" t="s">
         <v>76</v>
@@ -3139,24 +3145,24 @@
         <v>203</v>
       </c>
       <c r="N28" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="O28" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="Q28" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="R28" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
@@ -3171,7 +3177,7 @@
         <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="G29" t="s">
         <v>76</v>
@@ -3195,19 +3201,19 @@
         <v>204</v>
       </c>
       <c r="N29" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="O29" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="Q29" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="R29" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -3227,7 +3233,7 @@
         <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="G30" t="s">
         <v>76</v>
@@ -3251,19 +3257,19 @@
         <v>205</v>
       </c>
       <c r="N30" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="O30" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="s">
         <v>76</v>
       </c>
       <c r="R30" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31A65A9-DBDE-4A99-9F7B-CD914D29FE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976BF523-B51C-47CD-A99B-E8FA83E18216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30765" yWindow="1740" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3315" yWindow="675" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="398">
   <si>
     <t>SKU</t>
   </si>
@@ -1211,6 +1211,9 @@
   </si>
   <si>
     <t>£2756.16</t>
+  </si>
+  <si>
+    <t>£16.50</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1797,7 @@
         <v>48</v>
       </c>
       <c r="Q4" t="s">
-        <v>48</v>
+        <v>397</v>
       </c>
       <c r="R4" t="s">
         <v>49</v>
